--- a/docs/ai_log/AI_AuditLog_PhamPhuongThao.xlsx
+++ b/docs/ai_log/AI_AuditLog_PhamPhuongThao.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\CSD\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\CSD201_Group6\docs\ai_log\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="12380"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="12380" firstSheet="1" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="1. Metadata &amp; Summary" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="192">
   <si>
     <t>AI AUDIT LOG - METADATA &amp; SUMMARY</t>
   </si>
@@ -625,6 +625,9 @@
   </si>
   <si>
     <t>011</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
@@ -886,6 +889,18 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -905,18 +920,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1232,14 +1235,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
     </row>
     <row r="3" spans="1:6" ht="17.5">
       <c r="A3" s="12" t="s">
@@ -1472,28 +1475,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="36" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
-      <c r="H1" s="35"/>
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
+      <c r="G1" s="39"/>
+      <c r="H1" s="39"/>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1">
-      <c r="A2" s="34" t="s">
+      <c r="A2" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="B2" s="35"/>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
+      <c r="B2" s="39"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
+      <c r="G2" s="39"/>
+      <c r="H2" s="39"/>
     </row>
     <row r="3" spans="1:9" ht="40" customHeight="1">
       <c r="A3" s="8" t="s">
@@ -1677,7 +1680,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="10" spans="1:9" s="41" customFormat="1" ht="80" customHeight="1">
+    <row r="10" spans="1:9" s="33" customFormat="1" ht="80" customHeight="1">
       <c r="A10" s="5" t="s">
         <v>166</v>
       </c>
@@ -1699,12 +1702,12 @@
       <c r="G10" s="29" t="s">
         <v>163</v>
       </c>
-      <c r="H10" s="42" t="s">
+      <c r="H10" s="34" t="s">
         <v>164</v>
       </c>
-      <c r="I10" s="43"/>
-    </row>
-    <row r="11" spans="1:9" s="41" customFormat="1" ht="80" customHeight="1">
+      <c r="I10" s="35"/>
+    </row>
+    <row r="11" spans="1:9" s="33" customFormat="1" ht="80" customHeight="1">
       <c r="A11" s="5" t="s">
         <v>167</v>
       </c>
@@ -1726,11 +1729,11 @@
       <c r="G11" s="29" t="s">
         <v>172</v>
       </c>
-      <c r="H11" s="42" t="s">
+      <c r="H11" s="34" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="12" spans="1:9" s="41" customFormat="1" ht="80" customHeight="1">
+    <row r="12" spans="1:9" s="33" customFormat="1" ht="80" customHeight="1">
       <c r="A12" s="5" t="s">
         <v>168</v>
       </c>
@@ -1752,11 +1755,11 @@
       <c r="G12" s="29" t="s">
         <v>183</v>
       </c>
-      <c r="H12" s="42" t="s">
+      <c r="H12" s="34" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="13" spans="1:9" s="41" customFormat="1" ht="80" customHeight="1">
+    <row r="13" spans="1:9" s="33" customFormat="1" ht="80" customHeight="1">
       <c r="A13" s="5" t="s">
         <v>189</v>
       </c>
@@ -1778,11 +1781,11 @@
       <c r="G13" s="29" t="s">
         <v>181</v>
       </c>
-      <c r="H13" s="42" t="s">
+      <c r="H13" s="34" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="14" spans="1:9" s="41" customFormat="1" ht="80" customHeight="1">
+    <row r="14" spans="1:9" s="33" customFormat="1" ht="80" customHeight="1">
       <c r="A14" s="5" t="s">
         <v>190</v>
       </c>
@@ -1804,19 +1807,19 @@
       <c r="G14" s="29" t="s">
         <v>187</v>
       </c>
-      <c r="H14" s="42" t="s">
+      <c r="H14" s="34" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="15" spans="1:9" s="41" customFormat="1" ht="80" customHeight="1">
-      <c r="A15" s="40"/>
-      <c r="B15" s="40"/>
-      <c r="C15" s="40"/>
-      <c r="D15" s="40"/>
-      <c r="E15" s="40"/>
-      <c r="F15" s="40"/>
-      <c r="G15" s="40"/>
-      <c r="H15" s="40"/>
+    <row r="15" spans="1:9" s="33" customFormat="1" ht="80" customHeight="1">
+      <c r="A15" s="32"/>
+      <c r="B15" s="32"/>
+      <c r="C15" s="32"/>
+      <c r="D15" s="32"/>
+      <c r="E15" s="32"/>
+      <c r="F15" s="32"/>
+      <c r="G15" s="32"/>
+      <c r="H15" s="32"/>
     </row>
     <row r="16" spans="1:9" ht="80" customHeight="1">
       <c r="A16" s="3"/>
@@ -1939,24 +1942,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="42" t="s">
         <v>54</v>
       </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
-      <c r="E1" s="37"/>
-      <c r="F1" s="37"/>
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="36" t="s">
+      <c r="A2" s="40" t="s">
         <v>55</v>
       </c>
-      <c r="B2" s="37"/>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37"/>
+      <c r="B2" s="41"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
     </row>
     <row r="3" spans="1:8" ht="40" customHeight="1">
       <c r="A3" s="2" t="s">
@@ -2267,20 +2270,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="36" t="s">
         <v>81</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="39" t="s">
+      <c r="A2" s="43" t="s">
         <v>82</v>
       </c>
-      <c r="B2" s="33"/>
-      <c r="C2" s="33"/>
-      <c r="D2" s="33"/>
+      <c r="B2" s="37"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
     </row>
     <row r="4" spans="1:4" ht="17.5">
       <c r="A4" s="12" t="s">
@@ -2311,7 +2314,9 @@
       <c r="C6" s="20" t="s">
         <v>90</v>
       </c>
-      <c r="D6" s="21"/>
+      <c r="D6" s="21" t="s">
+        <v>191</v>
+      </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="20" t="s">

--- a/docs/ai_log/AI_AuditLog_PhamPhuongThao.xlsx
+++ b/docs/ai_log/AI_AuditLog_PhamPhuongThao.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="12380" firstSheet="1" activeTab="3"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="12380" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="1. Metadata &amp; Summary" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="197">
   <si>
     <t>AI AUDIT LOG - METADATA &amp; SUMMARY</t>
   </si>
@@ -512,9 +512,6 @@
 Decision Ownership: Quyết định sử dụng BenchmarkRunner mới vì kết quả ổn định hơn, giảm ảnh hưởng của JVM và phản ánh chính xác hơn hiệu năng của từng cấu trúc dữ liệu.</t>
   </si>
   <si>
-    <t>Evidence: So sánh BenchmarkRunner_old.java và BenchmarkRunner.java, kết quả benchmark nhiều round với median.</t>
-  </si>
-  <si>
     <t>Khi tăng số lượng updates mỗi phút lên rất cao, kết quả benchmark vẫn không xuất hiện trường hợp vượt ngưỡng 50ms như kỳ vọng.</t>
   </si>
   <si>
@@ -531,9 +528,6 @@
 </t>
   </si>
   <si>
-    <t>Evidence: Kết quả benchmark trước và sau khi thay đổi cách đánh giá ngưỡng.</t>
-  </si>
-  <si>
     <t>006</t>
   </si>
   <si>
@@ -562,9 +556,6 @@
 </t>
   </si>
   <si>
-    <t>Evidence: Đoạn mã cập nhật UPDATE_THRESHOLD_MS, kết quả benchmark sau khi sửa.</t>
-  </si>
-  <si>
     <t>Cần xác minh liệu số lượng 9 round benchmark có đủ để đảm bảo tính ổn định của kết quả hay không.</t>
   </si>
   <si>
@@ -572,9 +563,6 @@
   </si>
   <si>
     <t>AI giải thích rằng benchmark Java chịu ảnh hưởng bởi JIT Compilation, Garbage Collection và CPU Scheduling. Chạy nhiều round và lấy median sẽ giảm ảnh hưởng của các lần đo bất thường.</t>
-  </si>
-  <si>
-    <t>Evidence: Kết quả benchmark nhiều round và thống kê median của từng cấu trúc dữ liệu.</t>
   </si>
   <si>
     <t>Cần xây dựng flowchart cho hệ thống Smart Hospital. Ban đầu tôi đưa toàn bộ thuật toán của HashTable, Min-Heap, Circular Linked List và Doubly Linked List vào cùng một sơ đồ nên flowchart quá dài, khó đọc và trộn lẫn giữa nghiệp vụ với cài đặt.</t>
@@ -593,9 +581,6 @@
 </t>
   </si>
   <si>
-    <t>Evidence: Bộ flowchart sau khi tách thành nhiều sơ đồ nhỏ, mỗi sơ đồ chỉ mô tả một Use Case hoặc một thuật toán.</t>
-  </si>
-  <si>
     <t>Critical Thinking: AI giải thích đúng về median nhưng chưa chỉ rõ vì sao chọn số lẻ thay vì số chẵn.
 Contextualization: Benchmark của nhóm cần so sánh ba cấu trúc dữ liệu trong cùng điều kiện nên việc sử dụng median của 9 round giúp kết quả ổn định và dễ tái lập hơn.
 Creative Synthesis: Tôi giữ nguyên 9 round benchmark, đồng thời bổ sung phần giải thích trong báo cáo để làm rõ lý do lựa chọn median thay vì average.
@@ -618,9 +603,6 @@
 </t>
   </si>
   <si>
-    <t>Evidence: Phiên bản flowchart mới thể hiện các thao tác cập nhật cấu trúc dữ liệu theo chuỗi tuần tự thay vì ba nhánh song song.</t>
-  </si>
-  <si>
     <t>010</t>
   </si>
   <si>
@@ -628,6 +610,43 @@
   </si>
   <si>
     <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>Ban đầu tôi thiết kế một flowchart duy nhất mô tả toàn bộ hệ thống Smart Hospital, bao gồm tất cả actor, Use Case và thuật toán của các cấu trúc dữ liệu. Sơ đồ quá lớn, khó theo dõi và khó bảo trì khi cần chỉnh sửa.</t>
+  </si>
+  <si>
+    <t>"Hãy đánh giá flowchart hiện tại và đề xuất cách chia nhỏ thành nhiều flowchart nhưng vẫn đảm bảo thể hiện đầy đủ hoạt động của hệ thống."</t>
+  </si>
+  <si>
+    <t>AI đề xuất áp dụng phương pháp phân rã chức năng (functional decomposition), giữ một flowchart tổng quan mô tả các Use Case chính, sau đó tách riêng từng quy trình như Register Patient, Call Patient, Override Priority, Search Patient, View History và Delete Patient thành các flowchart độc lập. Thuật toán của từng cấu trúc dữ liệu được tách thành các sơ đồ riêng thay vì đặt chung trong luồng hệ thống.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Critical Thinking: AI đề xuất chia nhỏ flowchart nhưng chưa xác định rõ ranh giới giữa flow nghiệp vụ và flow thuật toán. Nếu chia không hợp lý sẽ dẫn đến trùng lặp nội dung giữa các sơ đồ.
+Contextualization: Dự án của nhóm sử dụng nhiều cấu trúc dữ liệu (Min-Heap, HashTable, Circular Linked List và Doubly Linked List). Mỗi cấu trúc đều có thuật toán riêng nên cần tách khỏi flow nghiệp vụ để người đọc dễ theo dõi và thuận tiện khi trình bày.
+Creative Synthesis: Tôi phân rã hệ thống thành một flowchart tổng quan và bảy flowchart Use Case, đồng thời dành các flowchart thuật toán riêng cho từng cấu trúc dữ liệu. Việc này giúp mỗi sơ đồ chỉ tập trung giải quyết một nhiệm vụ cụ thể và giảm đáng kể độ phức tạp.
+Decision Ownership: Quyết định cuối cùng là áp dụng phương pháp functional decomposition thay vì duy trì một flowchart duy nhất. Cách tổ chức này giúp tài liệu rõ ràng hơn, thuận lợi cho việc bảo vệ đồ án và dễ mở rộng khi bổ sung chức năng mới.
+</t>
+  </si>
+  <si>
+    <t>So sánh BenchmarkRunner_old.java và BenchmarkRunner.java, kết quả benchmark nhiều round với median.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Kết quả benchmark trước và sau khi thay đổi cách đánh giá ngưỡng.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Đoạn mã cập nhật UPDATE_THRESHOLD_MS, kết quả benchmark sau khi sửa.</t>
+  </si>
+  <si>
+    <t>Kết quả benchmark nhiều round và thống kê median của từng cấu trúc dữ liệu.</t>
+  </si>
+  <si>
+    <t>Bộ flowchart sau khi tách thành nhiều sơ đồ nhỏ, mỗi sơ đồ chỉ mô tả một Use Case hoặc một thuật toán.</t>
+  </si>
+  <si>
+    <t>Phiên bản flowchart mới thể hiện các thao tác cập nhật cấu trúc dữ liệu theo chuỗi tuần tự thay vì ba nhánh song song.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Bộ flowchart cuối cùng gồm 1 sơ đồ tổng quan hệ thống, 7 sơ đồ Use Case và các sơ đồ thuật toán riêng cho từng cấu trúc dữ liệu.</t>
   </si>
 </sst>
 </file>
@@ -818,7 +837,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -886,20 +905,14 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1235,14 +1248,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
-      <c r="E1" s="37"/>
-      <c r="F1" s="37"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
     </row>
     <row r="3" spans="1:6" ht="17.5">
       <c r="A3" s="12" t="s">
@@ -1412,7 +1425,7 @@
         <v>33</v>
       </c>
       <c r="B24" s="17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C24" s="18" t="s">
         <v>34</v>
@@ -1475,28 +1488,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="34" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="39"/>
-      <c r="H1" s="39"/>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="37"/>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1">
-      <c r="A2" s="38" t="s">
+      <c r="A2" s="36" t="s">
         <v>39</v>
       </c>
-      <c r="B2" s="39"/>
-      <c r="C2" s="39"/>
-      <c r="D2" s="39"/>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
-      <c r="G2" s="39"/>
-      <c r="H2" s="39"/>
+      <c r="B2" s="37"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
+      <c r="G2" s="37"/>
+      <c r="H2" s="37"/>
     </row>
     <row r="3" spans="1:9" ht="40" customHeight="1">
       <c r="A3" s="8" t="s">
@@ -1531,22 +1544,22 @@
       <c r="B4" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="33" t="s">
         <v>37</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="33" t="s">
         <v>118</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="33" t="s">
         <v>119</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="33" t="s">
         <v>120</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="G4" s="33" t="s">
         <v>136</v>
       </c>
-      <c r="H4" s="6" t="s">
+      <c r="H4" s="33" t="s">
         <v>121</v>
       </c>
     </row>
@@ -1560,19 +1573,19 @@
       <c r="C5" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="33" t="s">
         <v>123</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="F5" s="33" t="s">
         <v>124</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="G5" s="33" t="s">
         <v>137</v>
       </c>
-      <c r="H5" s="6" t="s">
+      <c r="H5" s="33" t="s">
         <v>125</v>
       </c>
     </row>
@@ -1580,25 +1593,25 @@
       <c r="A6" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="33" t="s">
         <v>53</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="33" t="s">
         <v>126</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E6" s="33" t="s">
         <v>127</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="F6" s="33" t="s">
         <v>128</v>
       </c>
-      <c r="G6" s="6" t="s">
+      <c r="G6" s="33" t="s">
         <v>138</v>
       </c>
-      <c r="H6" s="6" t="s">
+      <c r="H6" s="33" t="s">
         <v>129</v>
       </c>
     </row>
@@ -1612,7 +1625,7 @@
       <c r="C7" s="29" t="s">
         <v>35</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="33" t="s">
         <v>131</v>
       </c>
       <c r="E7" s="29" t="s">
@@ -1656,7 +1669,7 @@
     </row>
     <row r="9" spans="1:9" s="30" customFormat="1" ht="93.5" customHeight="1">
       <c r="A9" s="5" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B9" s="30" t="s">
         <v>139</v>
@@ -1664,7 +1677,7 @@
       <c r="C9" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="D9" s="31" t="s">
+      <c r="D9" s="33" t="s">
         <v>155</v>
       </c>
       <c r="E9" s="29" t="s">
@@ -1677,12 +1690,12 @@
         <v>158</v>
       </c>
       <c r="H9" s="29" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" s="33" customFormat="1" ht="80" customHeight="1">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" s="31" customFormat="1" ht="80" customHeight="1">
       <c r="A10" s="5" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B10" s="29" t="s">
         <v>51</v>
@@ -1691,25 +1704,25 @@
         <v>35</v>
       </c>
       <c r="D10" s="29" t="s">
+        <v>159</v>
+      </c>
+      <c r="E10" s="29" t="s">
         <v>160</v>
       </c>
-      <c r="E10" s="29" t="s">
+      <c r="F10" s="29" t="s">
         <v>161</v>
       </c>
-      <c r="F10" s="29" t="s">
+      <c r="G10" s="29" t="s">
         <v>162</v>
       </c>
-      <c r="G10" s="29" t="s">
-        <v>163</v>
-      </c>
-      <c r="H10" s="34" t="s">
-        <v>164</v>
-      </c>
-      <c r="I10" s="35"/>
-    </row>
-    <row r="11" spans="1:9" s="33" customFormat="1" ht="80" customHeight="1">
+      <c r="H10" s="29" t="s">
+        <v>191</v>
+      </c>
+      <c r="I10" s="32"/>
+    </row>
+    <row r="11" spans="1:9" s="31" customFormat="1" ht="80" customHeight="1">
       <c r="A11" s="5" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B11" s="29" t="s">
         <v>53</v>
@@ -1718,24 +1731,24 @@
         <v>37</v>
       </c>
       <c r="D11" s="29" t="s">
+        <v>167</v>
+      </c>
+      <c r="E11" s="29" t="s">
+        <v>168</v>
+      </c>
+      <c r="F11" s="29" t="s">
         <v>169</v>
       </c>
-      <c r="E11" s="29" t="s">
+      <c r="G11" s="29" t="s">
         <v>170</v>
       </c>
-      <c r="F11" s="29" t="s">
-        <v>171</v>
-      </c>
-      <c r="G11" s="29" t="s">
-        <v>172</v>
-      </c>
-      <c r="H11" s="34" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" s="33" customFormat="1" ht="80" customHeight="1">
+      <c r="H11" s="29" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" s="31" customFormat="1" ht="80" customHeight="1">
       <c r="A12" s="5" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B12" s="29" t="s">
         <v>53</v>
@@ -1744,24 +1757,24 @@
         <v>36</v>
       </c>
       <c r="D12" s="29" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="E12" s="29" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="F12" s="29" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="G12" s="29" t="s">
+        <v>178</v>
+      </c>
+      <c r="H12" s="29" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" s="31" customFormat="1" ht="80" customHeight="1">
+      <c r="A13" s="5" t="s">
         <v>183</v>
-      </c>
-      <c r="H12" s="34" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" s="33" customFormat="1" ht="80" customHeight="1">
-      <c r="A13" s="5" t="s">
-        <v>189</v>
       </c>
       <c r="B13" s="29" t="s">
         <v>139</v>
@@ -1770,24 +1783,24 @@
         <v>36</v>
       </c>
       <c r="D13" s="29" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="E13" s="29" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="F13" s="29" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="G13" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="H13" s="34" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" s="33" customFormat="1" ht="80" customHeight="1">
+        <v>177</v>
+      </c>
+      <c r="H13" s="29" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" s="31" customFormat="1" ht="80" customHeight="1">
       <c r="A14" s="5" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="B14" s="29" t="s">
         <v>53</v>
@@ -1796,30 +1809,44 @@
         <v>37</v>
       </c>
       <c r="D14" s="29" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="E14" s="29" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="F14" s="29" t="s">
+        <v>181</v>
+      </c>
+      <c r="G14" s="29" t="s">
+        <v>182</v>
+      </c>
+      <c r="H14" s="29" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" s="31" customFormat="1" ht="80" customHeight="1">
+      <c r="A15" s="29"/>
+      <c r="B15" s="29" t="s">
+        <v>139</v>
+      </c>
+      <c r="C15" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="D15" s="29" t="s">
         <v>186</v>
       </c>
-      <c r="G14" s="29" t="s">
+      <c r="E15" s="29" t="s">
         <v>187</v>
       </c>
-      <c r="H14" s="34" t="s">
+      <c r="F15" s="29" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="15" spans="1:9" s="33" customFormat="1" ht="80" customHeight="1">
-      <c r="A15" s="32"/>
-      <c r="B15" s="32"/>
-      <c r="C15" s="32"/>
-      <c r="D15" s="32"/>
-      <c r="E15" s="32"/>
-      <c r="F15" s="32"/>
-      <c r="G15" s="32"/>
-      <c r="H15" s="32"/>
+      <c r="G15" s="29" t="s">
+        <v>189</v>
+      </c>
+      <c r="H15" s="29" t="s">
+        <v>196</v>
+      </c>
     </row>
     <row r="16" spans="1:9" ht="80" customHeight="1">
       <c r="A16" s="3"/>
@@ -1942,24 +1969,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="42" t="s">
+      <c r="A1" s="40" t="s">
         <v>54</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="40" t="s">
+      <c r="A2" s="38" t="s">
         <v>55</v>
       </c>
-      <c r="B2" s="41"/>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
+      <c r="B2" s="39"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
     </row>
     <row r="3" spans="1:8" ht="40" customHeight="1">
       <c r="A3" s="2" t="s">
@@ -2270,20 +2297,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="34" t="s">
         <v>81</v>
       </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="43" t="s">
+      <c r="A2" s="41" t="s">
         <v>82</v>
       </c>
-      <c r="B2" s="37"/>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
+      <c r="B2" s="35"/>
+      <c r="C2" s="35"/>
+      <c r="D2" s="35"/>
     </row>
     <row r="4" spans="1:4" ht="17.5">
       <c r="A4" s="12" t="s">
@@ -2315,7 +2342,7 @@
         <v>90</v>
       </c>
       <c r="D6" s="21" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="7" spans="1:4">
